--- a/logs/log_ejecucion.xlsx
+++ b/logs/log_ejecucion.xlsx
@@ -437,7 +437,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:04:14</t>
+          <t>2026-10-28 17:17:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -454,17 +454,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 16:04:15</t>
+          <t>2026-10-28 17:17:42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reporte creado: salida\carga_novedades.xlsx</t>
+          <t>Error: [Errno 13] Permission denied: 'salida\\carga_novedades.xlsx'</t>
         </is>
       </c>
     </row>

--- a/logs/log_ejecucion.xlsx
+++ b/logs/log_ejecucion.xlsx
@@ -437,7 +437,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:17:42</t>
+          <t>2026-10-29 10:58:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -454,17 +454,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 17:17:42</t>
+          <t>2026-10-29 10:58:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Error: [Errno 13] Permission denied: 'salida\\carga_novedades.xlsx'</t>
+          <t>Reporte creado: salida\carga_novedades.xlsx</t>
         </is>
       </c>
     </row>

--- a/logs/log_ejecucion.xlsx
+++ b/logs/log_ejecucion.xlsx
@@ -437,7 +437,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:58:43</t>
+          <t>2026-10-29 15:28:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -454,7 +454,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:58:44</t>
+          <t>2026-10-29 15:28:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
